--- a/public/CA_Importing_Template.xlsx
+++ b/public/CA_Importing_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A3115B2-F6A6-48A5-BE9B-D22233B71A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{432BECC5-EFC8-4F0C-8EFE-8300BD0C919D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Date From</t>
   </si>
@@ -67,27 +67,6 @@
   </si>
   <si>
     <t>Destination</t>
-  </si>
-  <si>
-    <t>Butuan City</t>
-  </si>
-  <si>
-    <t>James E. Rosales</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>AGRISTAT</t>
-  </si>
-  <si>
-    <t>Melody C. Guimary</t>
-  </si>
-  <si>
-    <t>Chief</t>
-  </si>
-  <si>
-    <t>Field Operations Division</t>
   </si>
 </sst>
 </file>
@@ -157,14 +136,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -484,13 +460,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CAD3974-0F7B-413B-9962-A1A83CE8234D}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="27.46484375" style="1" customWidth="1"/>
     <col min="2" max="2" width="21.46484375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3984375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="10.86328125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="11.3984375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="10.86328125" style="4" customWidth="1"/>
     <col min="5" max="5" width="23.06640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.06640625" style="1"/>
     <col min="7" max="7" width="22.33203125" style="1" customWidth="1"/>
@@ -531,38 +507,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="4">
-        <v>46294</v>
-      </c>
-      <c r="D2" s="4">
-        <v>46296</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/CA_Importing_Template.xlsx
+++ b/public/CA_Importing_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{432BECC5-EFC8-4F0C-8EFE-8300BD0C919D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B1B3F0-864A-43B9-A038-0798CE70F44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
@@ -138,13 +138,15 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -463,47 +465,48 @@
   <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="27.46484375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.46484375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3984375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="10.86328125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="23.06640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.06640625" style="1"/>
-    <col min="7" max="7" width="22.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="21.59765625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.9296875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="21.53125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="27.46484375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="21.46484375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="11.3984375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="10.86328125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="23.06640625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="9.06640625" style="3"/>
+    <col min="7" max="7" width="22.33203125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="21.59765625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="18.9296875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="21.53125" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="9.06640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:10" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
     </row>

--- a/public/CA_Importing_Template.xlsx
+++ b/public/CA_Importing_Template.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B1B3F0-864A-43B9-A038-0798CE70F44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80D65F8-E1BF-4AAA-B1B7-9CA98D254467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="15661" windowHeight="9848" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Appearance" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/public/CA_Importing_Template.xlsx
+++ b/public/CA_Importing_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80D65F8-E1BF-4AAA-B1B7-9CA98D254467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC79162-9C16-4F9F-B50B-48C14004A594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="15661" windowHeight="9848" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Appearance" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Date From</t>
   </si>
@@ -54,19 +54,13 @@
     <t>Office</t>
   </si>
   <si>
-    <t>Signatory Name</t>
-  </si>
-  <si>
-    <t>Designation</t>
-  </si>
-  <si>
-    <t>Division</t>
-  </si>
-  <si>
     <t>Title</t>
   </si>
   <si>
     <t>Destination</t>
+  </si>
+  <si>
+    <t>Division Name</t>
   </si>
 </sst>
 </file>
@@ -462,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CAD3974-0F7B-413B-9962-A1A83CE8234D}">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="27.46484375" style="3" customWidth="1"/>
@@ -472,18 +466,16 @@
     <col min="5" max="5" width="23.06640625" style="3" customWidth="1"/>
     <col min="6" max="6" width="9.06640625" style="3"/>
     <col min="7" max="7" width="22.33203125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="21.59765625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="18.9296875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="21.53125" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="9.06640625" style="4"/>
+    <col min="8" max="8" width="21.53125" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="9.06640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
@@ -501,12 +493,6 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
     </row>

--- a/public/CA_Importing_Template.xlsx
+++ b/public/CA_Importing_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC79162-9C16-4F9F-B50B-48C14004A594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76482E3D-7EA1-4911-84D5-46C5E22A31E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
@@ -60,7 +60,7 @@
     <t>Destination</t>
   </si>
   <si>
-    <t>Division Name</t>
+    <t>Signatory Division</t>
   </si>
 </sst>
 </file>
@@ -466,7 +466,7 @@
     <col min="5" max="5" width="23.06640625" style="3" customWidth="1"/>
     <col min="6" max="6" width="9.06640625" style="3"/>
     <col min="7" max="7" width="22.33203125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="21.53125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="24.265625" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9.06640625" style="4"/>
   </cols>
   <sheetData>

--- a/public/CA_Importing_Template.xlsx
+++ b/public/CA_Importing_Template.xlsx
@@ -8,13 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76482E3D-7EA1-4911-84D5-46C5E22A31E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E43A436-5B34-4889-9F4F-230308107A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
+    <workbookView xWindow="1718" yWindow="1718" windowWidth="15659" windowHeight="9847" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Appearance" sheetId="1" r:id="rId1"/>
+    <sheet name="Division" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="Division">Table1[[#All],[Division]]</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Date From</t>
   </si>
@@ -61,6 +65,36 @@
   </si>
   <si>
     <t>Signatory Division</t>
+  </si>
+  <si>
+    <t>Administrative Division</t>
+  </si>
+  <si>
+    <t>Division</t>
+  </si>
+  <si>
+    <t>Agribusiness and Marketing Assistance Division</t>
+  </si>
+  <si>
+    <t>Field Operations Division</t>
+  </si>
+  <si>
+    <t>Integrated Laboratories Division</t>
+  </si>
+  <si>
+    <t>Regional Agricultural Engineering Division</t>
+  </si>
+  <si>
+    <t>Regulatory Division</t>
+  </si>
+  <si>
+    <t>Research Division</t>
+  </si>
+  <si>
+    <t>Planning, Monitoring and Evaluation Division</t>
+  </si>
+  <si>
+    <t>Finance Division</t>
   </si>
 </sst>
 </file>
@@ -130,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -141,6 +175,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -157,6 +194,16 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DF3C0830-9077-46CF-8D5F-ECBCB37B3F0E}" name="Table1" displayName="Table1" ref="A1:A10" totalsRowShown="0">
+  <autoFilter ref="A1:A10" xr:uid="{DF3C0830-9077-46CF-8D5F-ECBCB37B3F0E}"/>
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{A4A956AD-A026-47EB-B051-91CA7D1BD730}" name="Division"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -497,6 +544,84 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="The inputted date is out of the coverage." sqref="C2:D1048576" xr:uid="{34CAC791-D6B5-43AC-9D15-8CA0F70D9089}">
+      <formula1>46023</formula1>
+      <formula2>46752</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Invalid Input." sqref="F2:F1048576" xr:uid="{4681846F-60E8-423A-A3EC-080338F3A873}">
+      <formula1>"Male, Female"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Invalid input." sqref="H2:H1048576" xr:uid="{AF13CCBD-83AD-4683-8318-71490B70B7E6}">
+      <formula1>Division</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41C79C4C-5C8F-481F-AF09-35EA5DD839CC}">
+  <dimension ref="A1:A10"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="40.265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A2" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/public/CA_Importing_Template.xlsx
+++ b/public/CA_Importing_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E43A436-5B34-4889-9F4F-230308107A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402EFBFD-C01C-4A16-814B-D5A810DF4F5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1718" yWindow="1718" windowWidth="15659" windowHeight="9847" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Appearance" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>Date From</t>
   </si>
@@ -64,9 +64,6 @@
     <t>Destination</t>
   </si>
   <si>
-    <t>Signatory Division</t>
-  </si>
-  <si>
     <t>Administrative Division</t>
   </si>
   <si>
@@ -95,6 +92,9 @@
   </si>
   <si>
     <t>Finance Division</t>
+  </si>
+  <si>
+    <t>Unit / Program / Project</t>
   </si>
 </sst>
 </file>
@@ -164,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -178,6 +178,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -503,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CAD3974-0F7B-413B-9962-A1A83CE8234D}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="27.46484375" style="3" customWidth="1"/>
@@ -512,12 +515,13 @@
     <col min="4" max="4" width="10.86328125" style="3" customWidth="1"/>
     <col min="5" max="5" width="23.06640625" style="3" customWidth="1"/>
     <col min="6" max="6" width="9.06640625" style="3"/>
-    <col min="7" max="7" width="22.33203125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="24.265625" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="9.06640625" style="4"/>
+    <col min="7" max="8" width="22.33203125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="24.265625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="25.06640625" style="6" customWidth="1"/>
+    <col min="11" max="16384" width="9.06640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -540,7 +544,13 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -552,11 +562,12 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Invalid Input." sqref="F2:F1048576" xr:uid="{4681846F-60E8-423A-A3EC-080338F3A873}">
       <formula1>"Male, Female"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Invalid input." sqref="H2:H1048576" xr:uid="{AF13CCBD-83AD-4683-8318-71490B70B7E6}">
-      <formula1>Division</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="The input is invalid." sqref="H2:H1048576" xr:uid="{0A5262DD-0E87-47CD-AAF5-9B3988B9F02F}">
+      <formula1>"Division, Office of the Regional Executive Director"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -570,52 +581,52 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/public/CA_Importing_Template.xlsx
+++ b/public/CA_Importing_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402EFBFD-C01C-4A16-814B-D5A810DF4F5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAA919DD-3D58-4D72-AEB3-7486BA19D568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{28108F55-8346-401A-B717-A4C0635FECEB}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Division" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="Division">Table1[[#All],[Division]]</definedName>
+    <definedName name="Division">Division!$A$2:$A$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>Date From</t>
   </si>
@@ -49,12 +49,6 @@
     <t>Date To</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Gender</t>
-  </si>
-  <si>
     <t>Office</t>
   </si>
   <si>
@@ -95,6 +89,18 @@
   </si>
   <si>
     <t>Unit / Program / Project</t>
+  </si>
+  <si>
+    <t>Attendee Name</t>
+  </si>
+  <si>
+    <t>Attendee Gender</t>
+  </si>
+  <si>
+    <t>Attendee Office</t>
+  </si>
+  <si>
+    <t>Signatory Division</t>
   </si>
 </sst>
 </file>
@@ -123,7 +129,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -133,6 +139,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -164,9 +182,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -179,8 +196,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -506,55 +538,71 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CAD3974-0F7B-413B-9962-A1A83CE8234D}">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="27.46484375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="21.46484375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="11.3984375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="10.86328125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="23.06640625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="9.06640625" style="3"/>
-    <col min="7" max="8" width="22.33203125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="24.265625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="25.06640625" style="6" customWidth="1"/>
-    <col min="11" max="16384" width="9.06640625" style="4"/>
+    <col min="1" max="2" width="35.59765625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.19921875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.86328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.06640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="22.796875" style="2" customWidth="1"/>
+    <col min="7" max="8" width="22.33203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="24.265625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="25.06640625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="42" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9.06640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" s="5" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="J1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="The inputted date is out of the coverage." sqref="C2:D1048576" xr:uid="{34CAC791-D6B5-43AC-9D15-8CA0F70D9089}">
       <formula1>46023</formula1>
       <formula2>46752</formula2>
@@ -564,6 +612,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="The input is invalid." sqref="H2:H1048576" xr:uid="{0A5262DD-0E87-47CD-AAF5-9B3988B9F02F}">
       <formula1>"Division, Office of the Regional Executive Director"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Choose a listed DA signatory division." promptTitle="Signatory Division" prompt="Choose a DA signatory division; leave blank when certificate Division is listed." sqref="K2:K1048576" xr:uid="{00000000-0002-0000-0000-000003000000}">
+      <formula1>Division</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -581,52 +632,52 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A2" s="5" t="s">
-        <v>7</v>
+      <c r="A2" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
